--- a/resources/protocol_template.xlsx
+++ b/resources/protocol_template.xlsx
@@ -14,6 +14,9 @@
   <sheets>
     <sheet name="Сертификат" sheetId="5" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Сертификат!$A$1:$AC$98</definedName>
+  </definedNames>
   <calcPr calcId="162913" fullPrecision="0"/>
 </workbook>
 </file>
@@ -2184,10 +2187,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/activeX/activeX1.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D7053240-CE69-11CD-A777-00DD01143C57}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2294,51 +2293,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица2" displayName="Таблица2" ref="A2:E30" totalsRowShown="0" headerRowBorderDxfId="35" tableBorderDxfId="34" totalsRowBorderDxfId="33">
-  <autoFilter ref="A2:E30"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Наименование организации" dataDxfId="32" dataCellStyle="Обычный 3"/>
-    <tableColumn id="2" name="ИНН" dataDxfId="31" dataCellStyle="Обычный 3"/>
-    <tableColumn id="4" name="Столбец1" dataDxfId="30" dataCellStyle="Обычный 3">
-      <calculatedColumnFormula>CONCATENATE(Таблица2[[#This Row],[Наименование организации]],", ИНН ",Таблица2[[#This Row],[ИНН]])</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="6" name="Договор" dataDxfId="29" dataCellStyle="Обычный 3"/>
-    <tableColumn id="3" name="Столбец2" dataCellStyle="Обычный 3"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Таблица3" displayName="Таблица3" ref="F2:Y14" totalsRowShown="0" headerRowDxfId="28" headerRowBorderDxfId="27" tableBorderDxfId="26" totalsRowBorderDxfId="25" headerRowCellStyle="Обычный 3" dataCellStyle="Обычный 3">
-  <autoFilter ref="F2:Y14"/>
-  <tableColumns count="20">
-    <tableColumn id="1" name="Тип" dataDxfId="24" dataCellStyle="Обычный 3"/>
-    <tableColumn id="30" name="Наименование аппаратуры" dataDxfId="23" dataCellStyle="Обычный 3"/>
-    <tableColumn id="17" name="P1" dataDxfId="22" dataCellStyle="Обычный 3"/>
-    <tableColumn id="16" name="P2" dataDxfId="21" dataCellStyle="Обычный 3"/>
-    <tableColumn id="15" name="P3" dataDxfId="20" dataCellStyle="Обычный 3"/>
-    <tableColumn id="14" name="P4" dataDxfId="19" dataCellStyle="Обычный 3"/>
-    <tableColumn id="11" name="P5" dataDxfId="18" dataCellStyle="Обычный 3"/>
-    <tableColumn id="4" name="ед. изм. P" dataDxfId="17" dataCellStyle="Обычный 3"/>
-    <tableColumn id="5" name="Погрешность Абс/Отн P" dataDxfId="16" dataCellStyle="Обычный 3"/>
-    <tableColumn id="28" name="значение погрешности P" dataDxfId="15" dataCellStyle="Обычный 3"/>
-    <tableColumn id="6" name="ед. изм. Погрешности P" dataDxfId="14" dataCellStyle="Обычный 3"/>
-    <tableColumn id="19" name="T1" dataDxfId="13" dataCellStyle="Обычный 3"/>
-    <tableColumn id="20" name="T2" dataDxfId="12" dataCellStyle="Обычный 3"/>
-    <tableColumn id="21" name="T3" dataDxfId="11" dataCellStyle="Обычный 3"/>
-    <tableColumn id="22" name="T4" dataDxfId="10" dataCellStyle="Обычный 3"/>
-    <tableColumn id="23" name="T5" dataDxfId="9" dataCellStyle="Обычный 3"/>
-    <tableColumn id="24" name="ед. изм. T" dataDxfId="8" dataCellStyle="Обычный 3"/>
-    <tableColumn id="25" name="Погрешность Абс/Отн T" dataDxfId="7" dataCellStyle="Обычный 3"/>
-    <tableColumn id="29" name="значение погрешности T" dataDxfId="6" dataCellStyle="Обычный 3"/>
-    <tableColumn id="26" name="ед. изм. Погрешности T" dataDxfId="5" dataCellStyle="Обычный 3"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4473,21 +4427,6 @@
     <mergeCell ref="K13:S13"/>
     <mergeCell ref="K17:AB17"/>
   </mergeCells>
-  <conditionalFormatting sqref="A73:C77">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J73:L77">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S73:U77">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K17:AB17">
       <formula1>Заказчик</formula1>
@@ -4506,77 +4445,5 @@
     <brk id="60" max="27" man="1"/>
   </rowBreaks>
   <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
-  <controls>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="2050" r:id="rId4" name="CommandButton1">
-          <controlPr defaultSize="0" autoLine="0" autoPict="0" r:id="rId5">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>20</xdr:col>
-                <xdr:colOff>38100</xdr:colOff>
-                <xdr:row>10</xdr:row>
-                <xdr:rowOff>66675</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>27</xdr:col>
-                <xdr:colOff>190500</xdr:colOff>
-                <xdr:row>13</xdr:row>
-                <xdr:rowOff>28575</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="2050" r:id="rId4" name="CommandButton1"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-  </controls>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="44" operator="notBetween" id="{D2454AF0-E142-4FB7-9555-E7FA765E3156}">
-            <xm:f>-Исх.данные!$AJ$3</xm:f>
-            <xm:f>Исх.данные!$AJ$3</xm:f>
-            <x14:dxf>
-              <font>
-                <b/>
-                <i val="0"/>
-                <color rgb="FFC00000"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFFFF00"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>G73:I77 P73:R77 Y73:AA77</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="41" operator="notBetween" id="{1109AC7C-78D8-47F4-8FEA-7DA77C74A916}">
-            <xm:f>-Исх.данные!$AS$3</xm:f>
-            <xm:f>Исх.данные!$AS$3</xm:f>
-            <x14:dxf>
-              <font>
-                <b/>
-                <i val="0"/>
-                <color rgb="FFFF0000"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFFFF00"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>G86:J88</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
--- a/resources/protocol_template.xlsx
+++ b/resources/protocol_template.xlsx
@@ -13,10 +13,8 @@
   </bookViews>
   <sheets>
     <sheet name="Сертификат" sheetId="5" r:id="rId2"/>
+    <sheet name="_proto" sheetId="6" state="veryHidden" r:id="rId100"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Сертификат!$A$1:$AC$98</definedName>
-  </definedNames>
   <calcPr calcId="162913" fullPrecision="0"/>
 </workbook>
 </file>
@@ -2191,64 +2189,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>20</xdr:col>
-          <xdr:colOff>38100</xdr:colOff>
-          <xdr:row>10</xdr:row>
-          <xdr:rowOff>66675</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>27</xdr:col>
-          <xdr:colOff>190500</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2050" name="CommandButton1" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2050"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -2269,7 +2209,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:srcRect t="-1" r="55170" b="3166"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
@@ -2583,7 +2522,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист1"/>
-  <dimension ref="A1:AC97"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr defaultColWidth="3.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -3687,6 +3626,60 @@
       <c r="X46" s="8"/>
       <c r="Y46" s="8"/>
     </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="K30:N30"/>
+    <mergeCell ref="I27:S27"/>
+    <mergeCell ref="I26:S26"/>
+    <mergeCell ref="I28:S28"/>
+    <mergeCell ref="T27:U27"/>
+    <mergeCell ref="T26:U26"/>
+    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="K19:U19"/>
+    <mergeCell ref="A7:AC7"/>
+    <mergeCell ref="P9:S9"/>
+    <mergeCell ref="P1:AC5"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="K13:S13"/>
+    <mergeCell ref="K17:AB17"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K17:AB17">
+      <formula1>Заказчик</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K13">
+      <formula1>Тип_аппаратуры</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="75" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;RПротокол № 322-26 от 24.07.2026        стр &amp;P из &amp;N</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,обычный"&amp;8Протокол о калибровке не может быть воспроизведен полностью или частично без письменного разрешения ООО "НГС"</oddFooter>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="60" max="27" man="1"/>
+  </rowBreaks>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A61:AC97"/>
+  <sheetFormatPr defaultColWidth="3.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="6" max="6" width="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="3.42578125" customWidth="1"/>
+    <col min="13" max="13" width="3.5703125" customWidth="1"/>
+    <col min="20" max="20" width="3.42578125" customWidth="1"/>
+    <col min="30" max="30" width="3.42578125" customWidth="1"/>
+    <col min="34" max="34" width="3.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
     <row r="61" spans="1:29" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A61" s="120" t="s">
         <v>7</v>
@@ -4332,14 +4325,7 @@
       <c r="AC97" s="144"/>
     </row>
   </sheetData>
-  <mergeCells count="93">
-    <mergeCell ref="K30:N30"/>
-    <mergeCell ref="I27:S27"/>
-    <mergeCell ref="I26:S26"/>
-    <mergeCell ref="I28:S28"/>
-    <mergeCell ref="T27:U27"/>
-    <mergeCell ref="T26:U26"/>
-    <mergeCell ref="T28:U28"/>
+  <mergeCells count="77">
     <mergeCell ref="Y73:AA73"/>
     <mergeCell ref="D73:F73"/>
     <mergeCell ref="S73:U73"/>
@@ -4356,7 +4342,6 @@
     <mergeCell ref="Z97:AC97"/>
     <mergeCell ref="K96:O96"/>
     <mergeCell ref="R96:X96"/>
-    <mergeCell ref="K15:M15"/>
     <mergeCell ref="A92:AC94"/>
     <mergeCell ref="Z96:AC96"/>
     <mergeCell ref="A87:C87"/>
@@ -4418,32 +4403,7 @@
     <mergeCell ref="S71:U71"/>
     <mergeCell ref="V71:X71"/>
     <mergeCell ref="Y71:AA71"/>
-    <mergeCell ref="K19:U19"/>
-    <mergeCell ref="A7:AC7"/>
-    <mergeCell ref="P9:S9"/>
-    <mergeCell ref="P1:AC5"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="K13:S13"/>
-    <mergeCell ref="K17:AB17"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K17:AB17">
-      <formula1>Заказчик</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K13">
-      <formula1>Тип_аппаратуры</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="85" orientation="portrait" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;RПротокол № 322-26 от 24.07.2026        стр &amp;P из &amp;N</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,обычный"&amp;8Протокол о калибровке не может быть воспроизведен полностью или частично без письменного разрешения ООО "НГС"</oddFooter>
-  </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="60" max="27" man="1"/>
-  </rowBreaks>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>